--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_07_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_07_19_Cau.xlsx
@@ -611,7 +611,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
@@ -625,7 +629,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính sample volume trước rồi nhân unit cost.</t>
+          <t>Chi phí eval hàng ngày: 1.000.000 requests * 1% sample rate * 0,002 USD/sampled request = 10.000 requests * 0,002 USD = 20 USD/ngày.</t>
         </is>
       </c>
     </row>
@@ -707,7 +711,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Quality failure candidate, Feedback hoặc judge evidence.</t>
+          <t>Khi một trường hợp lỗi ở production có chứa dữ liệu nhạy cảm PII, quy trình đưa vào tập kiểm thử offline bắt buộc là phải làm sạch (sanitize/redact) dữ liệu PII và được chuyên gia thẩm định trước khi lưu trữ.</t>
         </is>
       </c>
     </row>
@@ -789,7 +793,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Judge identity/version, Score distribution.</t>
+          <t>Khi điểm số của LLM judge sụt giảm sau khi nâng cấp phiên bản nhưng độ đồng thuận của judge với nhãn chuyên gia cũng giảm, bước đầu tiên là phải kiểm tra sự lệch lạc của chính bộ đánh giá (evaluator drift).</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1005,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Personal-data flow, Processor/vendor.</t>
+          <t>Khi dữ liệu cá nhân của người dùng Việt Nam được chuyển ra máy chủ nước ngoài mà chưa rõ điều khoản xử lý dữ liệu và căn cứ pháp lý, hành động đúng là gắn cờ cảnh báo để đội ngũ pháp lý rà soát tuân thủ.</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1221,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Span anomaly, Baseline comparison.</t>
+          <t>Dữ liệu trace cho thấy bước retrieval chậm nhưng chưa có thông tin về triển khai thay đổi hay kiểm chứng khắc phục; quan sát này mới chỉ cấu thành một giả thuyết nguyên nhân (cause candidate) chứ chưa phải kết luận gốc rễ.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_07_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_07_19_Cau.xlsx
@@ -660,10 +660,29 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Sampling population, Evaluator identity/version.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Sampling population, Evaluator identity/version.</t>
+- 1.0đ: Thiết kế vòng lặp pipeline hoàn chỉnh từ lấy mẫu bất đồng bộ đến phát thải Prometheus metric có cấu trúc.
+- 1.0đ: Thiết lập quy tắc cảnh báo PromQL phát hiện sụt giảm điểm chất lượng trong cửa sổ thời gian trượt.
+- 1.0đ: Bắt buộc gắn thẻ phiên bản giám khảo bất biến (judge_version label) trên mọi metric.
+- 1.0đ: Thiết lập cơ chế chạy đối chứng song song (dual-running calibration) để phân biệt giữa lỗi hệ thống và sự thay đổi độ khắt khe của judge.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Vòng lặp Biến Đánh giá Lấy mẫu thành Metric Giám sát (Sampled Eval-to-Metric Loop) có Quản lý Phiên bản Giám khảo (Judge Versioning):
+1. **Kiến trúc Vòng lặp Lấy mẫu sang Metric (Sampling-to-Metric Pipeline)**:
+- **Lấy mẫu bất đồng bộ (Async Queue)**: Lấy mẫu 2-5% traffic sản xuất, đẩy vào Kafka topic `eval-sampling-stream`.
+- **Worker Đánh giá (Eval Evaluator)**: Chạy mô hình LLM-as-a-Judge đánh giá trên các tiêu chí chuẩn (ví dụ: `groundedness`, `answer_relevance`) với thang điểm từ 0.0 đến 1.0.
+- **Chuyển hóa thành Time-series Metric**: Định kỳ gom cụm (15 phút một lần), tính toán điểm số trung bình và phát thải thành metric Prometheus:
+  `llm_online_eval_score{feature='chat', model_version='v2.1', judge_version='j1.4', metric_name='faithfulness'}`.
+2. **Cơ chế Cảnh báo Sụt giảm Chất lượng (Quality Drop Alert)**:
+- Thiết lập cảnh báo dựa trên PromQL:
+  `avg_over_time(llm_online_eval_score{metric_name='faithfulness'}[1h]) &lt; 0.80`.
+  Nếu điểm số chất lượng rơi xuống dưới 0.80 liên tục trong 1 giờ, kích hoạt cảnh báo Warning cho AI Engineering Team.
+3. **Quản trị Phiên bản Giám khảo (Judge Versioning Governance)**:
+- **Gắn thẻ phiên bản bắt buộc (Immutable Judge Tagging)**: Metric bắt buộc phải chứa nhãn `judge_version`. Khi nâng cấp prompt của judge hoặc đổi mô hình judge từ GPT-4o sang Claude-3.5-Sonnet, nhãn này bắt buộc phải tăng (e.g., `j1.4` -&gt; `j2.0`).
+- **Ngăn chặn Cảnh báo Giả khi đổi Judge (Dual-running / Calibration Window)**:
+  Khi nâng cấp Judge, chạy song song cả `judge_version=j1.4` và `j2.0` trên cùng một tập mẫu trong 48 giờ.   Thiết lập ngưỡng cảnh báo riêng cho `j2.0` sau khi đã hiệu chỉnh đường cơ sở (re-baselining), tuyệt đối không so sánh trực tiếp điểm số thô của hai phiên bản judge khác nhau vì sự thay đổi điểm có thể chỉ do judge mới khắt khe hơn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sử dụng LLM-as-a-Judge để giám sát thời gian thực là bước tiến lớn của AI Observability, nhưng tiềm ẩn rủi ro 'người chấm thi bị trôi dạt' (Evaluator Drift). Nếu không quản lý phiên bản giám khảo (Judge Versioning), một sự sụt giảm điểm số trên dashboard có thể bị hiểu nhầm là ứng dụng AI bị lỗi, trong khi thực chất chỉ là do ai đó vừa cập nhật prompt của giám khảo khiến nó chấm gắt hơn. Gắn thẻ phiên bản và chạy đối chứng song song là nguyên tắc bắt buộc để bảo toàn tính trung thực của số liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangSmith Documentation: Online Evaluation &amp; Datadog: Monitoring LLM Judges in Production</t>
         </is>
       </c>
     </row>
@@ -742,10 +761,25 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Quality failure candidate, Feedback hoặc judge evidence.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Quality failure candidate, Feedback hoặc judge evidence.</t>
+- 1.0đ: Phân tích và loại bỏ chính xác ca Outage mạng tạm thời, giải thích rủi ro gây flaky test.
+- 1.0đ: Lựa chọn và bảo vệ xác đáng việc thăng hạng ca Prompt Regression có thể tái lập vào Golden Suite.
+- 1.0đ: Liệt kê đầy đủ các thành phần dữ liệu bằng chứng bắt buộc phải lưu giữ (input, context, negative output, golden truth).
+- 1.0đ: Lưu giữ đầy đủ metadata môi trường thực thi (model version, temperature, trace link) để tái lập chuẩn xác trong CI/CD.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Ca lỗi để Thăng hạng (Selection for Regression Suite Promotion):
+- **Ca lỗi 1: Outage Tạm thời của Provider (Temporary Network Outage / 503)** -&gt; **KHÔNG THĂNG HẠNG (DO NOT PROMOTE)**.
+  *Lý do*: Lỗi mạng hạ tầng tạm thời không phản ánh hợp đồng sản phẩm (product contract) và không bắt nguồn từ logic nội tại của ứng dụng. Đưa ca này vào bộ test hồi quy tự động chỉ làm tốn thời gian chạy test vô ích và gây báo động giả (flaky test).
+- **Ca lỗi 2: Hồi quy do Sửa Prompt (Reproducible Prompt Regression)** -&gt; **BẮT BUỘC THĂNG HẠNG (PROMOTE TO GOLDEN SUITE)**.
+  *Lý do*: Đây là lỗi suy giảm logic nghiệp vụ cốt lõi có thể tái lập 100% (deterministic/reproducible). Khi prompt bị sửa đổi, model đã vi phạm một ràng buộc nghiệp vụ quan trọng. Ca này bắt buộc phải trở thành một bài kiểm thử cố định trong CI/CD để vĩnh viễn ngăn chặn lỗi này tái phát trong tương lai.
+2. Bằng chứng Cần Lưu giữ Nguyên trạng (Evidence Package to Preserve):
+- **Bộ dữ liệu đầu vào nguyên bản**: Toàn bộ chuỗi hội thoại của người dùng (`input_messages`), system prompt tại thời điểm lỗi, và tài liệu context được retrieval trả về.
+- **Đầu ra lỗi thực tế (Negative Output)**: Câu trả lời sai lệch mà mô hình đã sinh ra trên production để làm đối chứng.
+- **Đáp án Chuẩn mực Vàng (Golden Ground Truth)**: Câu trả lời chính xác được chuyên gia con người thẩm định hoặc tiêu chí chấp nhận định lượng (Assertions / Rubric cụ thể).
+- **Metadata Môi trường**: Phiên bản model (`gpt-4o-2024-08-06`), nhiệt độ `temperature`, seed, và liên kết trace ID ban đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Bộ Kiểm thử Hồi quy Sản xuất (Production-to-Regression Promotion Loop): Không phải mọi sự cố production đều xứng đáng đưa vào bộ test hồi quy. Các sự cố ngẫu nhiên về mạng hoặc hạ tầng đám mây thuộc về tầng quan sát SRE. Chỉ những ca lỗi logic suy luận có thể tái lập do thay đổi prompt, thay đổi embedding hoặc thay đổi logic agent mới cần được 'thăng hạng' thành một Golden Test Case trong CI/CD. Một bằng chứng đầy đủ (input, context, negative output, golden assertion) bảo đảm ca test có giá trị bảo vệ lâu dài.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Hamel Husain: Creating a Golden Dataset for LLMs &amp; Martin Fowler: Continuous Delivery and Test Suites</t>
         </is>
       </c>
     </row>
@@ -824,10 +858,28 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Judge identity/version, Score distribution.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Judge identity/version, Score distribution.</t>
+- 1.0đ: Nhận diện chính xác bài toán nhiễu biến số khi cả đối tượng đo và công cụ đo cùng thay đổi đồng thời.
+- 1.0đ: Thiết kế ma trận kiểm thử trực giao 2x2 sử dụng một Golden Benchmark bất biến làm đối chứng.
+- 1.0đ: Thiết lập công thức đo lường độc lập Evaluator Drift (so sánh hai judge trên golden set cố định).
+- 1.0đ: Thiết lập công thức đo lường độc lập Product Drift (so sánh hai tập sản phẩm dưới cùng một judge cố định).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Kiểm định Tách biệt Trôi dạt Giám khảo (Evaluator Drift) và Trôi dạt Sản phẩm (Product Drift):
+1. **Bản chất Thách thức Đối ngẫu (Confounded Drift Problem)**:
+Khi cả tập câu trả lời sản xuất (Product Answers) và phiên bản giám khảo (Judge Version) cùng thay đổi đồng thời, sự sụt giảm điểm số trên dashboard có thể do Model sinh câu trả lời kém đi (Product Drift), HOẶC do Judge mới chấm thi khắt khe hơn (Evaluator Drift). Cần một ma trận kiểm định trực giao 2x2 để phân tách tuyệt đối.
+2. **Thiết kế Ma trận Kiểm tra Trực giao 2x2 (Orthogonal 2x2 Test Matrix)**:
+- Thiết lập một **Golden Benchmark Bất biến (Fixed Curated Baseline Dataset)** gồm 200 câu hỏi và câu trả lời chuẩn mực đã được con người duyệt kỹ.
+- Thực hiện 4 phép chấm điểm song song:
+  + **Cell 1**: `Judge Cũ` chấm trên `Golden Baseline Bất biến` -&gt; Điểm chuẩn $S_{11}$ (Baseline cố định, ví dụ: 0.90).
+  + **Cell 2**: `Judge Mới` chấm trên `Golden Baseline Bất biến` -&gt; Điểm $S_{21}$.
+  + **Cell 3**: `Judge Cũ` chấm trên `Production Answers Mới` -&gt; Điểm $S_{12}$.
+  + **Cell 4**: `Judge Mới` chấm trên `Production Answers Mới` -&gt; Điểm $S_{22}$.
+3. **Công thức Suy diễn Độc lập &amp; Kết luận**:
+- **Đo lường Evaluator Drift**: So sánh Cell 2 và Cell 1 trên cùng một tập Golden không đổi: $\Delta_{\text{judge}} = S_{21} - S_{11}$. Nếu $\Delta_{\text{judge}} = -0.12$, khẳng định **Giám khảo mới chấm khắt khe hơn 12%**.
+- **Đo lường Product Drift**: So sánh Cell 3 và Cell 1 dưới cùng một Giám khảo cũ: $\Delta_{\text{product}} = S_{12} - S_{11}$. Nếu $\Delta_{\text{product}} \approx 0$, khẳng định **Sản phẩm hoàn toàn không bị suy thoái**, sự sụt giảm điểm số trên dashboard 100% bắt nguồn từ việc đổi phiên bản Judge.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Khử Nhiễu Biến số (Confounding Variable Decoupling): Trong khoa học đo lường (Metrology), không bao giờ được phép thay đổi đồng thời cả vật thể đo và thước đo. Nếu cả hai cùng đổi, thước đo bị biến dạng sẽ làm sai lệch kết quả đánh giá vật thể. Bằng cách đưa một 'vật mẫu chuẩn bất biến' (Fixed Golden Baseline) vào ma trận kiểm thử trực giao 2x2, chúng ta có thể cô lập hoàn toàn sai số của thước đo (Evaluator Drift) ra khỏi sự thay đổi thực tế của đối tượng được đo (Product Drift).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Rasch Measurement Theory &amp; Chip Huyen: Designing Machine Learning Systems (Evaluation Drift &amp; Calibration)</t>
         </is>
       </c>
     </row>
@@ -954,10 +1006,22 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Data-class retention, TTL.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Data-class retention, TTL.</t>
+- 1.0đ: Gán đúng hợp đồng lưu trữ và bảo vệ nghiêm ngặt cho Raw Traces (7-14 ngày, truy cập hẹp on-call, xóa theo GDPR).
+- 1.0đ: Gán đúng hợp đồng cho Redacted Logs (30-90 ngày, truy cập rộng hơn cho dev, vòng đời ILM).
+- 1.0đ: Gán đúng hợp đồng cho Aggregate Metrics (12-15 tháng, downsampling, công khai nội bộ).
+- 1.0đ: Gán đúng hợp đồng kiểm toán tuân thủ cho Access Events (1-3 năm, WORM storage bất biến, cấm xóa trước hạn).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Gán Hợp đồng Lưu trữ, Truy cập, Xóa bỏ và Kiểm toán (Retention, Access, Deletion, Audit Contracts) cho 4 Loại Tài sản Telemetry:
+| Loại Tài sản Telemetry | Thời gian Lưu trữ (Retention) | Phân quyền Truy cập (Access Control) | Chính sách Xóa bỏ (Deletion Contract) | Hợp đồng Kiểm toán (Audit Logging) |
+| :--- | :--- | :--- | :--- | :--- |
+| **1. Raw Traces (Chứa đầy đủ spans &amp; metadata)** | **7 - 14 ngày** (Ngắn hạn phục vụ triage tức thì; chi phí lưu trữ cao). | Giới hạn nghiêm ngặt: Chỉ đội ngũ **Core SRE &amp; On-call Engineers** đang trong ca trực sự cố. | Tự động xóa cứng (hard delete / TTL purge) sau 14 ngày. Xóa theo yêu cầu GDPR trong vòng 48h. | Ghi log mọi thao tác truy vấn tìm kiếm hoặc xuất trace payload. |
+| **2. Redacted Logs (Log sự kiện đã khử khuẩn PII)** | **30 - 90 ngày** (Phục vụ phân tích xu hướng và post-mortem tháng). | Mở rộng: Toàn bộ **Kỹ sư Phần mềm (Devs &amp; QA)** trong tổ chức. | Tự động dọn dẹp theo chính sách vòng đời chỉ mục (ILM / Index Lifecycle Management). | Giám sát tần suất truy vấn hàng loạt ngăn ngừa rò rỉ dữ liệu diện rộng. |
+| **3. Aggregate Metrics (Chỉ số số học tổng hợp: Prometheus)** | **12 - 15 tháng** (Dung lượng nhẹ; phục vụ phân tích dung lượng và so sánh năm). | Công khai nội bộ: **Toàn bộ nhân sự** (Engineering, Product, Business). | Tự động hạ độ phân giải (downsampling từ 15s sang 1h sau 30 ngày) rồi lưu trữ lâu dài. | Không yêu cầu audit gắt gao do chỉ là các con số thống kê không danh tính. |
+| **4. Access Events (Nhật ký ai đọc dữ liệu nhạy cảm)** | **1 - 3 năm** (Bắt buộc theo chuẩn tuân thủ SOC2, ISO 27001, HIPAA). | Tuyệt mật: Chỉ **Security Operations Center (SOC) &amp; Compliance Officers**. | Lưu trên kho bất biến (WORM Storage, S3 Object Lock). **CẤM XÓA TRƯỚC HẠN**. | Tự thân nó là audit log; bất kỳ nỗ lực can thiệp nào đều phát cảnh báo bảo mật mức SEV-1. |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Quản trị Vòng đời Dữ liệu Telemetry (Data Governance in Observability): Không thể đối xử mọi loại telemetry như nhau. Raw traces có rủi ro lộ bí mật cao nhất nên phải có vòng đời ngắn nhất và truy cập hẹp nhất; Metrics là số liệu phi định danh nên có thể lưu trữ rất lâu với chi phí rẻ; và Access Events là bằng chứng pháp lý bắt buộc phải được bảo vệ trên hạ tầng bất biến (WORM) để chứng minh tính tuân thủ khi có thanh tra.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+NIST SP 800-92: Guide to Computer Security Log Management &amp; SOC 2 Trust Services Criteria (CC6: Logical Access Controls)</t>
         </is>
       </c>
     </row>
@@ -1036,10 +1100,28 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Personal-data flow, Processor/vendor.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Personal-data flow, Processor/vendor.</t>
+- 1.0đ: Trình bày khách quan các sự thật kỹ thuật về chuyển vùng địa lý (cross-region transfer) dựa trên bằng chứng mạng/DNS.
+- 1.0đ: Đánh giá chi tiết sự thay đổi tính năng lưu trữ và xóa dữ liệu giữa các phiên bản phần mềm.
+- 1.0đ: Giữ vững ranh giới chuyên môn kỹ thuật: tuyệt đối không đưa ra các phán quyết pháp lý mang tính khẳng định luật.
+- 1.0đ: Đưa ra các biện pháp giảm thiểu kỹ thuật thực tế (băm IP có muối, gateway filtering, định tuyến tạm thời).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Lập Báo cáo Đánh giá Tuân thủ Kỹ thuật khi Chuyển giao Telemetry (Technical Compliance Assessment Record):
+*(Lưu ý kỹ thuật: Tài liệu này cung cấp các sự thật kỹ thuật có thể kiểm chứng độc lập, không đưa ra kết luận pháp lý thay thế chuyên viên luật)*
+1. **Bản ghi Sự thật Kỹ thuật Chuyển giao Vùng Dữ liệu (Cross-region Technical Facts)**:
+- **Nhà cung cấp phụ (Subprocessor)**: Dịch vụ lưu trữ phân tích telemetry bên thứ ba (e.g., Datadog / OpenTelemetry Ingestion SaaS).
+- **Vùng chuyển đổi (Region Migration)**: Trước đây lưu trữ tại cụm `eu-west-1` (Frankfurt, EU); hiện tại cấu hình endpoint trỏ về `us-east-1` (Virginia, USA).
+- **Bằng chứng kỹ thuật kiểm chứng**: Phân tích DNS IP lookup và bản tin TLS Handshake xác nhận toàn bộ gói tin OTLP phát thải từ Collector đang kết nối tới IP thuộc dải mạng Bắc Mỹ (`us-east-1`).
+- **Tác động kỹ thuật**: Các gói tin telemetry chứa `customer_hash_id`, `ip_address`, và metadata hệ thống hiện đang rời khỏi phạm vi địa lý Liên minh Châu Âu (EU Data Residency Boundary).
+2. **Bản ghi Đánh giá Tính năng Lưu trữ theo Phiên bản (Versioned Retention Assessment)**:
+- **Phiên bản cũ (Collector v1.12 / Storage Tier Standard)**: Hỗ trợ cấu hình xóa tự động cứng sau 30 ngày (`retention_days = 30`) và có API hỗ trợ xóa theo yêu cầu `DeleteRecordByTraceID`.
+- **Phiên bản mới (Collector v2.0 / Cold Storage Tier)**: Tính năng lưu trữ lạnh (Cold Tier) tự động nén và đẩy dữ liệu vào kho lưu trữ thứ cấp với chu kỳ cố định 90 ngày; tính năng xóa tức thời theo từng trace ID đơn lẻ hiện **chưa khả dụng** trên phiên bản API này.
+3. **Biện pháp Giảm thiểu Kỹ thuật Khuyến nghị (Recommended Technical Mitigations)**:
+- Kích hoạt bộ lọc khử khuẩn cấp độ cao tại OpenTelemetry Gateway nội bộ: băm một chiều tất cả các địa chỉ IP thành `sha256(ip + daily_salt)` và loại bỏ triệt để mọi trường định danh người dùng trước khi gói tin rời khỏi gateway.
+- Tạm thời định tuyến dữ liệu sang cụm Collector nội bộ on-premise cho tới khi nhà cung cấp hoàn tất chứng thực kỹ thuật và hợp đồng xử lý dữ liệu (DPA).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Đánh giá Tuân thủ Kỹ thuật (Technical Compliance Assessment): Kỹ sư SRE không được phép đưa ra kết luận pháp lý (như 'hành vi này vi phạm GDPR'), nhưng có trách nhiệm ghi nhận chính xác 100% các sự thật khách quan về mặt mạng và phần mềm: địa chỉ IP máy chủ đích, biên giới truyền dữ liệu, sự thay đổi của các tính năng lưu trữ giữa các phiên bản, và đưa ra các giải pháp công nghệ (như băm IP, lọc gateway) để bảo vệ tổ chức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+ENISA Guidelines on Technical Measures for Data Security &amp; ISO/IEC 27018: Code of practice for protection of PII in public clouds</t>
         </is>
       </c>
     </row>
@@ -1170,10 +1252,25 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Metric time window, Symptom segmentation.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Metric time window, Symptom segmentation.</t>
+- 1.0đ: Xây dựng mắt xích 1 từ Metrics: khoanh vùng chuẩn xác khung giờ 09:00–09:20 và mức độ tăng P95.
+- 1.0đ: Xây dựng mắt xích 2 từ Logs: liên kết thành công mã yêu cầu đại diện req-77 và cảnh báo tương ứng.
+- 1.0đ: Xây dựng mắt xích 3 từ Traces: chứng minh span retrieval 4.2s chiếm ưu thế trên critical path.
+- 1.0đ: Đưa ra 2 bước kiểm tra kế tiếp cụ thể, có mục tiêu nhắm vào Vector DB (HNSW index, tham số top_k, bộ nhớ).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chuỗi Bằng chứng Hội tụ (Converging Evidence Chain from Metrics -&gt; Logs -&gt; Traces):
+- **Mắt xích 1 - Khoanh vùng từ Metrics (Time &amp; Macro Scope)**:
+  Metric `http_request_duration_seconds{quantile='0.95'}` ghi nhận đột biến từ 0.5s lên 5.2s chính xác trong khung giờ từ **09:00 đến 09:20**. Điều này khoanh vùng phạm vi thời gian xảy ra sự cố và xác nhận đây là vấn đề có hệ thống trong 20 phút chứ không phải lỗi ngẫu nhiên.
+- **Mắt xích 2 - Nhận diện từ Logs (Specific Correlation ID &amp; Micro Scope)**:
+  Truy vấn Loki logs trong khung giờ 09:00–09:20 phát hiện hàng loạt log cảnh báo `SlowQueryWarning` chứa mã định danh yêu cầu cụ thể: `request_id = 'req-77'` và `tenant_id = 'enterprise_beta'` kèm thông báo quá thời gian chờ xử lý.
+- **Mắt xích 3 - Xác định Nút thắt từ Traces (Critical Path &amp; Bottleneck Span)**:
+  Mở biểu đồ trace waterfall của `req-77` trên Jaeger/Tempo: Trace tổng thể mất 4.8s.   Trong đó, span `vector_db.retrieval_query` chiếm tới **4.2 giây** (chiếm gần 90% tổng thời gian request),   trong khi các span con khác như `llm_generation` chỉ mất 0.4s và `tool_execution` chỉ mất 0.1s.   Bằng chứng hội tụ khẳng định: **Nút thắt cổ chai nằm tại khâu truy vấn Vector Database**.
+2. Bước Kiểm tra Kế tiếp (Next Diagnostic Checks):
+- **Kiểm tra 1: Truy vấn Vector Database Logs &amp; Metrics**: Kiểm tra chỉ số `qdrant_search_duration_seconds` hoặc CPU/Memory của cụm Vector DB lúc 09:00–09:20 xem có bị full scan, lock contention, hoặc thiếu RAM dẫn đến disk-swapping không.
+- **Kiểm tra 2: Kiểm tra Tham số Truy vấn của req-77**: Kiểm tra xem `req-77` có truyền bộ lọc `filter` không đánh index, hoặc tham số `top_k` bị đẩy lên quá lớn (e.g., $k=500$ thay vì $k=5$) làm tê liệt thuật toán HNSW search hay không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Phương pháp Điều tra Sự cố Tam Giác (Metrics-Logs-Traces Triage Triangle): Metrics chỉ ra thời điểm bắt đầu và kết thúc (09:00–09:20); Logs cung cấp mã định danh cụ thể (req-77); và Traces chỉ ra chính xác span nào trên đường găng đang 'nuốt trọn' thời gian (retrieval span 4.2s). Sự hội tụ của ba bằng chứng này lập tức loại trừ các nghi phạm khác (như mạng chậm, LLM bị treo) và hướng thẳng mũi điều tra vào hạ tầng Vector Database.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry: Correlating Metrics, Logs, and Traces &amp; Google SRE Book: Diagnosing System Problems</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1349,25 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Span anomaly, Baseline comparison.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Span anomaly, Baseline comparison.</t>
+- 1.0đ: Phân tích sự ăn khớp về trình tự thời gian giữa lúc đổi config (08:55) và lúc bùng phát lỗi (09:00).
+- 1.0đ: Giải thích thỏa đáng cơ chế kỹ thuật vì sao bỏ index filter làm tăng độ phức tạp tính toán và độ trễ.
+- 1.0đ: Khẳng định sức mạnh chứng minh của bằng chứng can thiệp khôi phục (reversal proof khi restore filter).
+- 1.0đ: Nhận diện và chỉ rõ các yếu tố bất định còn lại (độ trễ 5 phút, lưu lượng nền đồng thời) cần tiếp tục đối soát.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Bằng chứng Hội tụ (Evaluation of Converging Root-Cause Evidence):
+- **Bằng chứng Thời gian Tuyệt đối (Temporal Precedence &amp; Correlation)**:
+  Sự thay đổi cấu hình diễn ra lúc **08:55** (bỏ bộ lọc index filter). Đúng 5 phút sau (**09:00**), khi traffic tích lũy và cache cũ hết hạn, P95 latency lập tức tăng vọt. Mối quan hệ nhân quả về mặt thời gian là hoàn toàn ăn khớp.
+- **Cơ chế Kỹ thuật Phù hợp (Mechanism Plausibility)**:
+  Khi bỏ index filter, cơ chế tìm kiếm trong cơ sở dữ liệu/vector store bị buộc phải chuyển từ Index Scan sang **Full Table/Collection Scan**, làm độ phức tạp thuật toán tăng từ $O(\log N)$ lên $O(N)$, hoàn toàn giải thích thỏa đáng vì sao span truy vấn tăng vọt.
+- **Bằng chứng Khôi phục Đối chứng (Intervention &amp; Reversal Proof)**:
+  Đây là bằng chứng vàng có sức nặng nhất (Gold Standard of Causality): Khi đội ngũ khôi phục lại filter (restore index filter), thời gian thực thi của span và P95 latency của toàn hệ thống **lập tức hạ nhiệt trở về baseline bình thường**. Khả năng đảo ngược kết quả khi can thiệp khẳng định mối quan hệ nhân quả trực tiếp.
+2. Bất định Còn lại (Residual Uncertainty &amp; Unanswered Questions):
+- **Tại sao có độ trễ 5 phút (08:55 -&gt; 09:00)?**: Cần xác minh do bộ đệm connection pool, cache TTL, hay do một cron job kích hoạt lúc 09:00 làm bùng phát vấn đề.
+- **Tác động của Lưu lượng Nền**: Liệu nếu lưu lượng lúc 08:55 thấp hơn thì có biểu hiện lỗi không? Cần kiểm tra xem có sự gia tăng đột biến nào khác từ phía người dùng cùng xảy ra lúc 09:00 hay không (Confounding Traffic Spike).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Chứng minh Nguyên nhân Gốc trong SRE (Converging Evidence &amp; Reversibility): Để khẳng định một thay đổi là nguyên nhân gốc, kỹ sư cần thỏa mãn ba tiêu chí của Bradford Hill: Trình tự thời gian (Temporal precedence), Tính khả thi về cơ chế kỹ thuật (Plausibility), và Bằng chứng can thiệp khôi phục (Reversibility). Khi khôi phục cấu hình mà hệ thống lập tức bình phục, giả thuyết nhân quả đạt độ tin cậy trên 95%. Tuy nhiên, người làm SRE chuẩn mực vẫn phải ghi nhận các điểm chưa giải thích hết (residual uncertainty) để đề phòng các nguyên nhân kết hợp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Bradford Hill Criteria for Causality &amp; Google SRE Workbook: Incident Postmortems and Root Cause Analysis</t>
         </is>
       </c>
     </row>
@@ -1382,10 +1494,33 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Timeline, Impact.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Timeline, Impact.</t>
+- 1.0đ: Xây dựng cấu trúc Postmortem chuẩn mực gồm Tóm tắt tác động, Timeline chi tiết, và Phân tích nguyên nhân.
+- 1.0đ: Thể hiện văn hóa Blameless: tập trung vào lỗ hổng quy trình/hạ tầng thay vì đổ lỗi cho cá nhân.
+- 1.0đ: Phân tích thấu đáo cả hai điểm yếu: khâu cấu hình thiếu filter và khâu cảnh báo bị chậm trễ 25 phút.
+- 1.0đ: Lập danh sách Action Items cụ thể, có thể thực thi, có người sở hữu (owner) và thời hạn (deadline) rõ ràng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Khung Báo cáo Hậu kiểm Không quy trách nhiệm Cá nhân có Thể Hành động (Actionable Blameless Postmortem Skeleton):
+1. **Tóm tắt Sự cố &amp; Tác động (Executive Summary &amp; User Impact)**:
+- Thời gian diễn ra: 08:55 - 09:45 (Tổng thời lượng: 50 phút). Khách hàng chịu ảnh hưởng: Khoảng 3.500 người dùng gặp độ trễ P95 &gt; 5s.
+- Bản chất sự cố: Thay đổi cấu hình thiếu index filter khiến cơ sở dữ liệu bị full-scan; đồng thời hệ thống cảnh báo bị trễ 25 phút làm kéo dài thời gian phát hiện.
+2. **Dòng Thời gian Sự kiện (Timeline of Events)**:
+- `08:55`: Cấu hình mới được deploy lên production, vô tình lược bỏ tham số index filter.
+- `09:00`: Hệ thống bắt đầu suy thoái hiệu năng, P95 latency tăng từ 0.5s lên 5.2s.
+- `09:25`: Cảnh báo Alertmanager mới chính thức kích hoạt tới PagerDuty (trễ 25 phút do cửa sổ tính toán quá dài).
+- `09:30`: Kỹ sư on-call tiếp nhận, mở trace và phát hiện span retrieval tăng vọt.
+- `09:40`: Kỹ sư thực hiện rollback cấu hình, khôi phục lại index filter.
+- `09:45`: P95 latency trở về baseline 0.5s; sự cố được dập tắt hoàn toàn.
+3. **Phân tích Nguyên nhân Gốc Không đổ lỗi (Blameless Root Cause Analysis)**:
+- **Nguyên nhân tầng sâu 1 (Thiếu hàng rào bảo vệ CI)**: Quy trình CI/CD cho phép deploy cấu hình database mà không có bước kiểm tra tự động (schema/query plan validation) để chặn các câu truy vấn thiếu filter.
+- **Nguyên nhân tầng sâu 2 (Cấu hình Alert kém nhạy)**: Alert rule sử dụng cửa sổ tính toán trung bình 30 phút quá lớn kèm ngưỡng kích hoạt chưa tối ưu, dẫn đến độ trễ phát hiện (MTTD) lên tới 25 phút.
+4. **Hành động Khắc phục Cụ thể có Người chịu trách nhiệm (Action Items)**:
+- **Action 1 (Phòng ngừa)**: Viết linter và pre-commit hook chặn mọi truy vấn thiếu index filter trong CI/CD pipeline. (Owner: @dev-lead, Deadline: 7 ngày, Priority: P0).
+- **Action 2 (Phát hiện)**: Cấu hình lại Alert rule sử dụng thuật toán multiwindow burn-rate (cửa sổ 5m/30m) để phát hiện suy thoái P95 trong vòng dưới 3 phút. (Owner: @sre-oncall, Deadline: 3 ngày, Priority: P0).
+- **Action 3 (Vận hành)**: Bổ sung runbook chẩn đoán nhanh độ trễ Vector DB vào wiki nội bộ. (Owner: @data-eng, Deadline: 5 ngày, Priority: P1).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Hậu kiểm Không đổ lỗi (Blameless Postmortem Culture): Mục tiêu của postmortem không phải là tìm ra 'ai là người đã xóa filter' để trừng phạt, mà là tìm hiểu 'tại sao hệ thống lại cho phép một cấu hình thiếu sót được triển khai lên production mà không bị phát hiện?'. Một bản postmortem mẫu mực phải chuyển hóa các bài học đau đớn thành danh sách hành động (Action Items) cụ thể, có phân công rõ người phụ trách (owner) và thời hạn hoàn thành (deadline) để xây dựng hệ thống miễn dịch vững chắc cho tương lai.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Chapter 15 - Postmortem Culture: Learning from Failure (https://sre.google/sre-book/postmortem-culture/) &amp; Etsy's Debriefing Facilitation Guide</t>
         </is>
       </c>
     </row>
